--- a/data/trans_orig/IP16A12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>26842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>46734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>65894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75922</t>
+          <t>75970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109127</t>
+          <t>109236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126107</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24614</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47870</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58068</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45764</t>
+          <t>46971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75594</t>
+          <t>76007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141247</t>
+          <t>141504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134053</t>
+          <t>132846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152796</t>
+          <t>152715</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281247</t>
+          <t>280834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309991</t>
+          <t>310340</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8642</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4769</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13522</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5791</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9370</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20724</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24597</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19061</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15482</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21617</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>76,7%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26842</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>39610</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>44688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29366</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56761</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5756</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2761</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9711</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4785</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8301</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16870</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12915</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19865</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>74,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15131</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21525</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36090</t>
+          <t>35144</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13221</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14490</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6726</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4118</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8546</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70,09%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8827</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14180</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5461</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11434</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40917</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35564</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>44751</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>71867</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65894</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75970</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>39675</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>117882</t>
+          <t>80592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109236</t>
+          <t>74546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126489</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77328</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6269</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10539</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5021</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9503</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>17148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25901</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29107</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>24574</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20092</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27189</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>53764</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>44402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57996</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>29595</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>61550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33028</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>24826</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>42365</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>14971</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>35520</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36079</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46971</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76007</t>
+          <t>69281</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>130019</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>120682</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>138221</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>79,74%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>74,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>151355</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>141504</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>162053</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>79,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>143738</t>
+          <t>118428</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>110407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>152715</t>
+          <t>124431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>295093</t>
+          <t>248447</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280834</t>
+          <t>236151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>310340</t>
+          <t>259139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>163047</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>177024</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>305432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
